--- a/db/data/items.xlsx
+++ b/db/data/items.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pradeep\Desktop\storemgmt\db\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9214FE-8153-443C-85F4-1BEBE6331B8F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2BAF23-E9DC-4EBF-90AF-FD127C9D7142}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="3045" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="1" r:id="rId1"/>
@@ -11425,7 +11425,7 @@
     </row>
     <row r="467" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B467">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C467">
         <v>179</v>
@@ -11442,7 +11442,7 @@
     </row>
     <row r="468" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B468">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C468">
         <v>178</v>

--- a/db/data/items.xlsx
+++ b/db/data/items.xlsx
@@ -1,26 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pradeep\Desktop\storemgmt\db\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Desktop\storemgmt\db\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2BAF23-E9DC-4EBF-90AF-FD127C9D7142}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="3045" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="3045" windowWidth="15375" windowHeight="7875"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="1035">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="1089">
   <si>
     <t>id</t>
   </si>
@@ -3125,22 +3124,179 @@
   </si>
   <si>
     <t>temp_cat_id</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 20mm dia. 16 kgf/cm2  (PN16)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 25 mm dia. 12.5 kgf/cm2  (PN12.5)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 32 mm dia. 10 kgf/cm2  (PN10)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 32 mm dia. 12.5 kgf/cm2  (PN12.5)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 32 mm dia. 16 kgf/cm2  (PN16)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 40 mm dia. 10 kgf/cm2  (PN10)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 50 mm dia. 6 kgf/cm2  (PN6)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 50 mm dia. 10 kgf/cm2  (PN10)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 50 mm dia. 12.5 kgf/cm2  (PN12.5)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 50 mm dia. 16 kgf/cm2  (PN16)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 63mm dia. 6 kgf/cm2  (PN6)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 63mm dia. 10 kgf/cm2  (PN10)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 63mm dia. 12.5 kgf/cm2  (PN12.5)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 63mm dia. 16 kgf/cm2  (PN16)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 75 mm dia. 6 kgf/cm2  (PN6)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 75 mm dia. 10 kgf/cm2  (PN10)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 75 mm dia. 16 kgf/cm2  (PN16)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 90 mm dia. 6 kgf/cm2  (PN6)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 110 mm dia.6 kgf/cm2  (PN6)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 110 mm dia.16 kgf/cm2  (PN16)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 125 mm dia.6 kgf/cm2  (PN6)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 140 mm dia.6 kgf/cm2  (PN6)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 140 mm dia.16 kgf/cm2  (PN16)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 160 mm dia.6 kgf/cm2  (PN6)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 180 mm dia.6 kgf/cm2  (PN6)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 180 mm dia.12.5 kgf/cm2  (PN12.5)</t>
+  </si>
+  <si>
+    <t>HDPE Pipe 180 mm dia.16 kgf/cm2  (PN16)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप २० एम एम (PN16)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ३० एम एम (PN16)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ५० एम एम (PN16)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ६३ एम एम (PN16)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ७५ एम एम (PN16)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ११० एम एम (PN16)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप १४०एम एम (PN16)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप १८० एम एम (PN16)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप २५ एम एम (PN12.5)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ३२ एम एम (PN10)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ३२ एम एम (PN12.5)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ४० एम एम (PN10)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ५० एम एम (PN6)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ५० एम एम (PN10)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ५० एम एम (PN12.5)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ६३ एम एम (PN6)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ६३ एम एम (PN10)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ६३ एम एम (PN12.5)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ७५ एम एम (PN6)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ७५ एम एम (PN10)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ९० एम एम (PN6)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप ११० एम एम (PN6)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप १२५ एम एम (PN6)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप १४०एम एम (PN6)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप १६० एम एम (PN6)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप १८० एम एम (PN6)</t>
+  </si>
+  <si>
+    <t>एचडिपिइ पाइप १८० एम एम (PN12.5)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -3168,9 +3324,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3484,8 +3639,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F525"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F552"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.375" bestFit="1" customWidth="1"/>
@@ -8659,7 +8814,7 @@
       <c r="C304">
         <v>393</v>
       </c>
-      <c r="D304" s="1" t="s">
+      <c r="D304" t="s">
         <v>796</v>
       </c>
       <c r="E304" t="s">
@@ -12338,7 +12493,7 @@
         <v>1028</v>
       </c>
       <c r="F520">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="521" spans="2:6" x14ac:dyDescent="0.2">
@@ -12355,7 +12510,7 @@
         <v>492</v>
       </c>
       <c r="F521">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="522" spans="2:6" x14ac:dyDescent="0.2">
@@ -12372,7 +12527,7 @@
         <v>493</v>
       </c>
       <c r="F522">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="523" spans="2:6" x14ac:dyDescent="0.2">
@@ -12389,7 +12544,7 @@
         <v>494</v>
       </c>
       <c r="F523">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="524" spans="2:6" x14ac:dyDescent="0.2">
@@ -12406,7 +12561,7 @@
         <v>495</v>
       </c>
       <c r="F524">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="525" spans="2:6" x14ac:dyDescent="0.2">
@@ -12423,11 +12578,389 @@
         <v>496</v>
       </c>
       <c r="F525">
-        <v>47</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="526" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B526">
+        <v>36</v>
+      </c>
+      <c r="D526" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E526" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F526">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="527" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B527">
+        <v>36</v>
+      </c>
+      <c r="D527" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E527" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F527">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="528" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B528">
+        <v>36</v>
+      </c>
+      <c r="D528" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E528" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F528">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="529" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B529">
+        <v>36</v>
+      </c>
+      <c r="D529" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E529" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F529">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="530" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B530">
+        <v>36</v>
+      </c>
+      <c r="D530" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E530" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F530">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="531" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B531">
+        <v>36</v>
+      </c>
+      <c r="D531" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E531" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F531">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="532" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B532">
+        <v>36</v>
+      </c>
+      <c r="D532" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E532" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F532">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="533" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B533">
+        <v>36</v>
+      </c>
+      <c r="D533" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E533" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F533">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="534" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B534">
+        <v>36</v>
+      </c>
+      <c r="D534" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E534" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F534">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="535" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B535">
+        <v>36</v>
+      </c>
+      <c r="D535" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E535" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F535">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="536" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B536">
+        <v>36</v>
+      </c>
+      <c r="D536" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E536" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F536">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="537" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B537">
+        <v>36</v>
+      </c>
+      <c r="D537" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E537" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F537">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="538" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B538">
+        <v>36</v>
+      </c>
+      <c r="D538" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E538" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F538">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="539" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B539">
+        <v>36</v>
+      </c>
+      <c r="D539" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E539" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F539">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="540" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B540">
+        <v>36</v>
+      </c>
+      <c r="D540" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E540" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F540">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="541" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B541">
+        <v>36</v>
+      </c>
+      <c r="D541" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E541" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F541">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="542" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B542">
+        <v>36</v>
+      </c>
+      <c r="D542" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E542" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F542">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="543" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B543">
+        <v>36</v>
+      </c>
+      <c r="D543" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E543" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F543">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="544" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B544">
+        <v>36</v>
+      </c>
+      <c r="D544" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E544" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F544">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="545" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B545">
+        <v>36</v>
+      </c>
+      <c r="D545" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E545" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F545">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="546" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B546">
+        <v>36</v>
+      </c>
+      <c r="D546" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E546" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F546">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="547" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B547">
+        <v>36</v>
+      </c>
+      <c r="D547" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E547" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F547">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="548" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B548">
+        <v>36</v>
+      </c>
+      <c r="D548" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E548" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F548">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="549" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B549">
+        <v>36</v>
+      </c>
+      <c r="D549" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E549" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F549">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="550" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B550">
+        <v>36</v>
+      </c>
+      <c r="D550" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E550" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F550">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="551" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B551">
+        <v>36</v>
+      </c>
+      <c r="D551" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E551" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F551">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="552" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B552">
+        <v>36</v>
+      </c>
+      <c r="D552" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E552" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F552">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
